--- a/sitepreview/trust/StructureDefinition-COSEHeader.xlsx
+++ b/sitepreview/trust/StructureDefinition-COSEHeader.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.5</t>
+    <t>1.1.6</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-17T14:22:45+00:00</t>
+    <t>2024-12-19T12:46:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sitepreview/trust/StructureDefinition-COSEHeader.xlsx
+++ b/sitepreview/trust/StructureDefinition-COSEHeader.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.6</t>
+    <t>1.1.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-19T12:46:28+00:00</t>
+    <t>2024-12-20T06:07:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sitepreview/trust/StructureDefinition-COSEHeader.xlsx
+++ b/sitepreview/trust/StructureDefinition-COSEHeader.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.0</t>
+    <t>1.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-27T08:38:34+00:00</t>
+    <t>2026-02-03T22:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sitepreview/trust/StructureDefinition-COSEHeader.xlsx
+++ b/sitepreview/trust/StructureDefinition-COSEHeader.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T22:38:59+00:00</t>
+    <t>2026-02-04T13:15:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sitepreview/trust/StructureDefinition-COSEHeader.xlsx
+++ b/sitepreview/trust/StructureDefinition-COSEHeader.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:15:56+00:00</t>
+    <t>2026-02-04T15:17:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sitepreview/trust/StructureDefinition-COSEHeader.xlsx
+++ b/sitepreview/trust/StructureDefinition-COSEHeader.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T15:17:54+00:00</t>
+    <t>2026-02-04T18:55:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sitepreview/trust/StructureDefinition-COSEHeader.xlsx
+++ b/sitepreview/trust/StructureDefinition-COSEHeader.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="87">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.4.0</t>
+    <t>1.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T14:17:30+00:00</t>
+    <t>2026-04-27T07:32:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -229,6 +229,9 @@
   </si>
   <si>
     <t>Constraint(s)</t>
+  </si>
+  <si>
+    <t>Mapping: RIM Mapping</t>
   </si>
   <si>
     <t/>
@@ -245,6 +248,9 @@
   </si>
   <si>
     <t>Base</t>
+  </si>
+  <si>
+    <t>n/a</t>
   </si>
   <si>
     <t>COSEHeader.1</t>
@@ -571,7 +577,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ4"/>
+  <dimension ref="A1:AK4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="12.44140625" customWidth="true" bestFit="true"/>
@@ -609,6 +615,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
+    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -720,6 +727,9 @@
       <c r="AJ1" t="s" s="1">
         <v>71</v>
       </c>
+      <c r="AK1" t="s" s="1">
+        <v>72</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
@@ -730,26 +740,26 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L2" t="s" s="2">
         <v>9</v>
@@ -760,265 +770,274 @@
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="AK2" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="AK3" t="s" s="2">
+        <v>73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="AK4" t="s" s="2">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/sitepreview/trust/StructureDefinition-COSEHeader.xlsx
+++ b/sitepreview/trust/StructureDefinition-COSEHeader.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-27T07:32:49+00:00</t>
+    <t>2026-07-01T12:00:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
